--- a/高中/数学/输出/上海高中数学-考点公式清单.xlsx
+++ b/高中/数学/输出/上海高中数学-考点公式清单.xlsx
@@ -11,15 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="例题索引" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公式表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关系边" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关卡地图" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'考点总表'!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'例题索引'!$A$1:$E$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公式表'!$A$1:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'关系边'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'关卡地图'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'考点总表'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'例题索引'!$A$1:$E$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公式表'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'关系边'!$A$1:$D$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -842,8 +840,618 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>A-4.1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>幂函数</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>y = x² 和 y = 2ˣ 都是幂函数吗？</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>04-三类基本函数-单元四.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A-4.2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>指数函数</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>指数函数 y = aˣ 的值域是 ℝ 吗？</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>04-三类基本函数-单元四.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>对数函数</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>y = log₂x 与 y = 2ˣ 的图像关于哪条直线对称？</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>04-三类基本函数-单元四.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A-5.1</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>函数的概念与表示</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>f(x) = x² 与 g(t) = t² 是同一个函数吗？</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>05-函数性质与应用-单元五.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>函数的基本性质</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>奇函数如果在 x = 0 处有定义，f(0) 一定等于 0 吗？</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>05-函数性质与应用-单元五.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>A-5.3</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>函数的应用</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>函数 y = f(x) 的图像与 x 轴有交点，说明方程 f(x) = 0 有实数解吗？</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>05-函数性质与应用-单元五.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>反函数</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Ⅰ</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>偶函数有反函数吗？</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>05-函数性质与应用-单元五.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>任意角与弧度制</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>30° 与 390° 的终边相同吗？</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>06-三角比-单元六.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A-6.2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>三角比与同角关系、诱导公式</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>sin 150° = sin 30° 吗？</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>06-三角比-单元六.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>A-6.3</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>两角和差与二倍角公式</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>sin(α + β) = sin α + sin β 吗？</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>06-三角比-单元六.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>解三角形</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>已知两边和其中一边的对角，三角形一定唯一确定吗？</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>06-三角比-单元六.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>正弦函数、余弦函数的图像与性质</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>y = sin x 的对称轴是 x = kπ 吗？</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>07-三角函数-单元七.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A-7.2</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>函数 y = A sin(ωx + φ) 的图像</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>把 y = sin x 的图像先向左平移 π/3、再把横坐标缩短为原来的 1/2，与"先缩短再平移"，结果一样吗？</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>07-三角函数-单元七.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>正切函数的图像与性质</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>y = tan x 在整个定义域上是增函数吗？</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>07-三角函数-单元七.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -854,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1458,8 +2066,1142 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A-4.1</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>判断下列函数中哪些是幂函数：y = x³，y = 2ˣ，y = x⁻²，y = (x+1)²，y = √x。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>A-4.1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>比较下列各组数的大小： （1）1.5³ 与 1.7³； （2）0.7⁻² 与 0.8⁻²。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A-4.1</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>已知幂函数 f(x) = x^(m²−2m−3)（m ∈ ℤ）在 (0, +∞) 上是减函数，且图像关于 y 轴对称，求 m 的值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>A-4.2</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>比较下列各组数的大小： （1）1.7² 与 1.7³； （2）0.8⁻¹ 与 0.8⁻²。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A-4.2</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>解不等式 2^(x²−1) ≥ 4。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>A-4.2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>已知函数 f(x) = aˣ（a &gt; 0 且 a ≠ 1）在区间 [-1, 1] 上的最大值与最小值之差为 3/2，求 a 的值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>求函数 y = log₂(x − 1) 的定义域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>比较下列各组数的大小： （1）log₂3 与 log₂5； （2）设 a = 1/2，比较 logₐ3 与 logₐ5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>已知 f(x) = logₐ(2x − 1)，其中 a = 1/2。解不等式 f(x) &gt; 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A-5.1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>求函数 f(x) = √(x − 2) + 1/(x − 3) 的定义域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A-5.1</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>判断下列各组函数是否为同一个函数： （1）f(x) = x 与 g(x) = x²/x； （2）f(x) = x 与 h(x) = √(x²)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A-5.1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>已知分段函数 f(x) = x + 1（x &lt; 0），f(x) = x²（0 ≤ x &lt; 2），f(x) = 2x（x ≥ 2）。 （1）求 f(f(-2))；（2）若 f(a) = 3，求 a。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>判断 f(x) = x³ + x 的奇偶性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>用定义证明 f(x) = x² + 1 在 (-∞, 0] 上是严格减函数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>已知 f(x) 是定义在 (-1, 1) 上的奇函数，且在 (-1, 1) 上严格递减。解不等式 f(1 - a) + f(1 - a²) &lt; 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A-5.3</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>求函数 f(x) = x² - 2x - 3 的零点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>A-5.3</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>用二分法求 f(x) = x³ + x - 3 在区间 (1, 2) 内的零点近似值（精确到 0.1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>A-5.3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>某商场促销：一次购物标价不超过 500 元不予优惠；超过 500 元但不超过 1000 元的按 9 折；超过 1000 元的，前 1000 元按 9 折、超出部分按 7 折。设标价为 x 元，实付 y 元。 （1）写出 y 关于 x 的函数</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>求 y = 2x + 1 的反函数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>求 y = x²（x ≥ 0）的反函数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>已知 f(x) = x² - 2x（x ≤ 1）。 （1）求 f 的反函数；（2）求 f⁻¹(3)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>把 67°30′ 化为弧度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>已知扇形的半径为 6，圆心角为 60°，求它的弧长和面积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>已知 α 是第二象限角，判断 α/2 是第几象限角。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>A-6.2</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>求 sin 210°、cos 240°、tan 225° 的值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>A-6.2</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>已知 sin α = 3/5，且 α 是第二象限角，求 cos α 与 tan α。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>A-6.2</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>化简 [sin(π − α) · cos(2π − α)] / [cos(π + α) · sin(-α)]。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>A-6.3</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>求 sin 75° 的值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>A-6.3</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>已知 sin α = 3/5，α ∈ (π/2, π)，求 sin 2α 与 cos 2α。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>A-6.3</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>求函数 y = sin x + √3 cos x 的最大值，并求取得最大值时 x 的集合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>在 △ABC 中，A = 30°，B = 45°，a = 2，求 b。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>在 △ABC 中，a = 3，b = 4，C = 60°，求 c 与 △ABC 的面积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>在 △ABC 中，a = √3，b = √2，B = 45°，求 A 与 C。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>求 y = 2 sin x + 1 的最大值、最小值，以及取得最值时 x 的集合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>求 y = sin(2x − π/3) 的单调递增区间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>求函数 y = sin²x + sin x − 1 的值域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>A-7.2</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>求 y = 3 sin(2x + π/4) 的振幅、最小正周期与初相。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>A-7.2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>把 y = sin x 图像上各点的横坐标缩短为原来的 1/2（纵坐标不变），再向左平移 π/6，求所得函数的解析式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>A-7.2</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已知 f(x) = A sin(ωx + φ)（A &gt; 0，ω &gt; 0，|φ| &lt; π/2），其图像相邻两条对称轴的距离为 π/2，且图像经过点 (π/6, 2) 并在该点取得最大值。 （1）求 f(x) 的解析式；（2）求 f(x) 在 </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>求 y = tan(2x − π/4) 的定义域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>求 y = tan(x + π/3) 的最小正周期与单调递增区间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>解不等式 tan x ≥ 1。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1470,7 +3212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1709,17 +3451,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>x² &lt; a² ⟺</t>
+          <t>x² &lt; a² ⟺ |x| &lt; a</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>二次不等式</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>&lt; a</t>
+          <t>a &gt; 0</t>
         </is>
       </c>
     </row>
@@ -1912,8 +3654,845 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>y = xᵃ</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>幂函数定义</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>系数为 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>a &gt; 0 时 xᵃ 在 (0,+∞) 递增</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>幂函数单调性</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>x &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>y = aˣ，值域 (0,+∞)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>指数函数</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>a &gt; 0, a ≠ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>a &gt; 1 ⇒ aˣ 在 ℝ 上递增</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>指数函数单调性</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>a &gt; 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>y = logₐx，定义域 (0,+∞)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>对数函数</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>a &gt; 0, a ≠ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>y = logₐx 与 y = aˣ 关于 y = x 对称</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>互为反函数</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>a &gt; 0, a ≠ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>logₐx &gt; 0 ⟺ x &gt; 1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>对数与 0 比较</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>a &gt; 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>y = f(x)，x ∈ A</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>函数定义</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>每 x 对应唯一 y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>定义域相同且对应法则相同 ⇒ 同一函数</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>相同函数判定</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>x₁ &lt; x₂ ⇒ f(x₁) &lt; f(x₂)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>严格增</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>x₁, x₂ ∈ D</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>f(-x) = -f(x)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>奇函数</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>定义域关于原点对称</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>f(a)·f(b) &lt; 0</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>区间内存在零点</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>f 在 [a,b] 连续</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>f⁻¹(b) = a ⟺ f(a) = b</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>反函数对应</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>存在反函数</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>y = aˣ 与 y = logₐx 关于 y = x 对称</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>指对互反</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>a &gt; 0, a ≠ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>β = α + k·360°</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>终边相同的角</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>k ∈ ℤ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>l = |α|r，S = ½|α|r²</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>弧长与扇形面积</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>α 用弧度</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>sin²α + cos²α = 1</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>同角关系</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>任意角</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>sin(π − α) = sin α</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>诱导公式</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>任意角</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>sin(α ± β) = sin α cos β ± cos α sin β</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>和差正弦</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>任意角</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>cos 2α = 1 − 2sin²α</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>二倍角余弦</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>任意角</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>a sin α + b cos α = √(a² + b²) sin(α + φ)</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>辅助角</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>tan φ = b/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>a² = b² + c² − 2bc cos A</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>余弦定理</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>S = ½ab sin C</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>三角形面积</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>T = 2π/|ω|</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>正弦、余弦型周期</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>ω ≠ 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>sin x ∈ [-1, 1]</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>正弦值域</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>任意 x</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>增区间 [-π/2 + 2kπ, π/2 + 2kπ]</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>sin x 单调性</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>k ∈ ℤ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>对称轴 x = π/2 + kπ</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>sin x 对称性</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>k ∈ ℤ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>y = A sin(ωx + φ)</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>振幅、周期、初相</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>A &gt; 0, ω &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>先伸缩后平移，平移量 |φ/ω|</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>图像变换</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ω &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>T = π/|ω|</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>正切型周期</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ω ≠ 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>x ≠ π/2 + kπ</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>tan x 定义域</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>k ∈ ℤ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1924,7 +4503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2087,68 +4666,387 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>A-3.2</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>A-4.1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>递进（对数 → 幂函数）</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>A-4.1</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>A-4.2</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>派生（幂函数 → 指数函数）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A-4.2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>反函数（指数 ↔ 对数）</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>反函数（对数函数 → 反函数一般理论）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>三类基本函数 · 单元四</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A-4.3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>A-5.1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>递进（对数函数 → 函数一般概念）</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>A-5.1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>递进（概念 → 性质）</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>A-5.3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>综合（性质 → 应用）</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>A-5.2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>派生（单调性 → 反函数存在）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>A-5.4</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>延伸（反函数 → 弧度制与三角）</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>函数的性质与应用 · 单元五</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>A-6.2</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>递进（角与弧度 → 三角比定义）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>A-6.2</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>A-6.3</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>派生（同角关系 → 和差公式）</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>A-6.3</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>综合（恒等变换 → 解三角形）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>延伸（解三角形 → 三角函数图像）</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>三角比 · 单元六</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>A-6.4</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>延伸（解三角形 → 三角函数图像）</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>A-7.1</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>A-7.2</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>派生（图像性质 → 图像变换）</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A-7.2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>并列（正弦型 → 正切型）</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>延伸（三角函数 → 平面向量）</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>三角函数 · 单元七</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>单元</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>关</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>考点</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>难度</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>星级</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2179,7 +5077,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3 个单元 / 7 个考点 / 21 道例题 / 15 条公式</t>
+          <t>7 个单元 / 21 个考点 / 63 道例题 / 46 条公式</t>
         </is>
       </c>
     </row>
@@ -2203,7 +5101,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>考点总表按单元筛选；例题索引可当题库；公式表可打印成速查卡；关卡地图可做打卡</t>
+          <t>考点总表按单元筛选；例题索引可当题库；公式表可打印成速查卡</t>
         </is>
       </c>
     </row>

--- a/高中/数学/输出/上海高中数学-考点公式清单.xlsx
+++ b/高中/数学/输出/上海高中数学-考点公式清单.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'考点总表'!$A$1:$I$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'例题索引'!$A$1:$E$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公式表'!$A$1:$E$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'关系边'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'考点总表'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'例题索引'!$A$1:$E$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'公式表'!$A$1:$E$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'关系边'!$A$1:$D$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1450,8 +1450,876 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>向量的概念与线性运算</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>零向量有方向吗？</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>08-平面向量-单元八.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>A-8.2</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>向量的数量积</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>a⃗ · b⃗ 的结果是向量还是数？</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>08-平面向量-单元八.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A-8.3</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>向量的坐标表示</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>a⃗ = (1, 2)，b⃗ = (2, 4)，a⃗ ∥ b⃗ 吗？</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>08-平面向量-单元八.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>向量的应用</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>用向量能证明三点共线吗？</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>08-平面向量-单元八.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>复数的概念与四则运算</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>i² 等于 −1 还是 1？</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>09-复数-单元九.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>复数的几何意义</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>两个复数能比较大小吗？</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>09-复数-单元九.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>实系数一元二次方程与复数的三角形式</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>实系数一元二次方程在 Δ &lt; 0 时有实数根吗？</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>09-复数-单元九.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>平面及其基本性质</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>三个点一定确定一个平面吗？</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>10-空间直线与平面-单元十.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A-10.2</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>直线与直线的位置关系</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>空间中不相交的两条直线一定平行吗？</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>10-空间直线与平面-单元十.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A-10.3</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>直线与平面的位置关系</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>直线与平面平行，它与平面内的所有直线都不相交吗？</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>10-空间直线与平面-单元十.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>平面与平面的位置关系</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>两个平面平行，其中一个平面内的所有直线都平行于另一个平面吗？</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>10-空间直线与平面-单元十.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>柱体与锥体</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>同底等高的锥体体积是柱体体积的几分之几？</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>11-简单几何体-单元十一.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>A-11.2</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>多面体与旋转体</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>圆台是由什么平面图形旋转得到的？</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>11-简单几何体-单元十一.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>球</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>球的表面积是 4πR² 还是 2πR²？</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>11-简单几何体-单元十一.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>随机现象与样本空间</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>抛两枚硬币，样本空间里有几个样本点？</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>12-概率初步-单元十二.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A-12.2</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>古典概率</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>古典概型中，每个样本点被取到的机会都一样吗？</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>12-概率初步-单元十二.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>频率与概率、事件的独立性</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>频率就是概率吗？</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>12-概率初步-单元十二.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>总体、样本与抽样</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>抽样调查一定不如普查准确吗？</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>13-统计-单元十三.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A-13.2</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>统计图表</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>频率分布直方图里，小矩形的面积表示什么？</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>13-统计-单元十三.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>A-13.3</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>统计估计</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Ⅱ</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>平均数和中位数，哪个更容易被极端值"带跑"？</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>13-统计-单元十三.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1462,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3200,8 +4068,1628 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>判断下列说法的正误： （1）若 |a⃗| = |b⃗|，则 a⃗ = b⃗； （2）若 a⃗ ∥ b⃗，b⃗ ∥ c⃗，则 a⃗ ∥ c⃗； （3）零向量与任意向量共线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>在平行四边形 ABCD 中，用 AB⃗、AD⃗ 表示 AC⃗、BD⃗，以及对角线交点 O 对应的 AO⃗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>已知 m⃗、n⃗ 不共线，a⃗ = m⃗ + 2n⃗，b⃗ = 2m⃗ + λn⃗。若 a⃗ ∥ b⃗，求 λ 的值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>A-8.2</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>已知 |a⃗| = 2，|b⃗| = 3，a⃗ 与 b⃗ 的夹角为 60°，求 a⃗ · b⃗ 与 (a⃗ + b⃗) · (a⃗ − b⃗)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>A-8.2</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>已知 |a⃗| = 1，|b⃗| = 2，a⃗ · b⃗ = 1，求 |a⃗ + b⃗| 与 a⃗、b⃗ 的夹角。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>A-8.2</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>已知 |a⃗| = 2，|b⃗| = 1，a⃗ 与 b⃗ 的夹角为 60°，求 |a⃗ − 2b⃗|。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>A-8.3</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>已知 a⃗ = (3, 4)，b⃗ = (−1, 2)，求 a⃗ · b⃗、|a⃗|、|b⃗| 与 a⃗ + b⃗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>A-8.3</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>已知 a⃗ = (1, 2)，b⃗ = (x, −1)。 （1）若 a⃗ ⊥ b⃗，求 x；（2）若 a⃗ ∥ b⃗，求 x。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>A-8.3</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>已知 a⃗ = (1, 2)，b⃗ = (−3, 2)。当 k 为何值时，ka⃗ + b⃗ 与 a⃗ − 3b⃗ 平行？</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>已知 A(0, 0)，B(2, 1)，C(−1, 2)，证明 AB⃗ ⊥ AC⃗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>两个力 F⃗、G⃗ 的大小都是 10 N，夹角为 120°，求合力的大小与方向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>在 △ABC 中，AB⃗ = (2, 3)，AC⃗ = (1, k)。若 △ABC 是直角三角形，求 k 的值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>计算 (1 + 2i)(3 − i)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>计算 (1 + i)/(1 − i)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>已知复数 z 满足 z(1 + i) = 3 − i，求 z 与 |z|。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>已知 z = 3 − 4i，写出它对应的点与模。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>说明下列方程表示的图形： （1）|z| = 1；（2）|z − 1| = 2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>已知复数 z 满足 |z| = 1，求 |z − 2| 的最大值与最小值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>解方程 x² + 2x + 5 = 0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>已知实系数一元二次方程 x² + px + q = 0 的一个根是 1 + i，求 p、q。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>把 z = 1 + √3i 化为三角形式，并求 z³。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>判断下列说法的正误： （1）三点确定一个平面； （2）两条平行直线确定一个平面； （3）一条直线和一个点确定一个平面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>证明：两两相交且不共点的三条直线在同一个平面内。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>用基本性质证明：梯形是平面图形。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>A-10.2</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>在正方体 ABCD-A₁B₁C₁D₁ 中，与棱 AB 异面的棱有几条？</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>A-10.2</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>在棱长为 a 的正方体 ABCD-A₁B₁C₁D₁ 中，求异面直线 A₁B 与 AD₁ 所成的角。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>A-10.2</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>正四面体 ABCD 的棱长为 a，求相对棱 AB 与 CD 所成的角及它们之间的距离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>A-10.3</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>在正方体 ABCD-A₁B₁C₁D₁ 中，判断下列直线与平面 ABCD 的位置关系： （1）A₁B₁；（2）BB₁；（3）A₁B。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>A-10.3</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>在棱长为 2 的正方体 ABCD-A₁B₁C₁D₁ 中，求 A₁B 与平面 ABCD 所成的角。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>A-10.3</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>已知 PA ⊥ 平面 ABC，且 AB ⊥ BC，证明：BC ⊥ 平面 PAB。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>在正方体 ABCD-A₁B₁C₁D₁ 中，判断下列两个平面的位置关系： （1）平面 ABCD 与平面 A₁B₁C₁D₁； （2）平面 ABCD 与平面 ABB₁A₁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>在棱长为 2 的正方体 ABCD-A₁B₁C₁D₁ 中，求二面角 A₁-BD-A 的正切值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>在四棱锥 P-ABCD 中，底面 ABCD 是正方形，PA ⊥ 平面 ABCD。证明：平面 PAC ⊥ 平面 PBD。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>圆柱的底面半径为 2，高为 5，求它的侧面积与体积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>正四棱锥的底面边长为 2，高为 √3，求它的体积与斜高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>圆锥的母线长为 5，底面半径为 3，求它的侧面积与体积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>A-11.2</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>正四面体有 4 个面、6 条棱、4 个顶点，验证欧拉公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>A-11.2</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>圆台的上底面半径为 1，下底面半径为 3，高为 4，求它的母线长、侧面积与体积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>A-11.2</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>棱长为 2 的正方体截去一个角（截面经过三条棱的中点），求剩下多面体的面数、棱数、顶点数，并验证欧拉公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>球的半径为 3，求它的表面积与体积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>球的半径为 5，一个截面到球心的距离为 3，求这个截面的面积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>棱长为 2 的正方体的外接球表面积是多少？内切球体积是多少？</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>掷一枚骰子，写出样本空间，以及事件 A = "点数为偶数"。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>袋中有 2 个红球、1 个白球（球都有编号），从中任取 2 个球，写出样本空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>抛两枚硬币，事件 A = "至少有一个正面"，B = "恰好有一个正面"。写出样本空间，求 A ∩ B、A ∪ B，并判断 A 与 B 的关系。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>A-12.2</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>掷一枚骰子，求"点数为 3 的倍数"的概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>A-12.2</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>袋中有 3 个红球、2 个白球，从中任取 2 个球，求取到的都是红球的概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>A-12.2</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>从 1、2、3、4、5 中任取 2 个数，求两数之和为偶数的概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>甲、乙两人独立射击，命中率分别为 0.8 和 0.7，求两人都命中的概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>条件同上，求"恰有一人命中"的概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>某射手每次射击命中的概率为 0.6，各次射击相互独立。求射击 3 次至少命中 1 次的概率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>某校共有 1000 名学生，抽取 100 名进行调查。指出总体、样本与样本容量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>某校高一 400 人、高二 300 人、高三 300 人，用分层抽样抽取 100 人，求各层应抽的人数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>某总体共 2000 人，用分层抽样抽取一个样本。已知某一层有 500 人，被抽到 25 人，求样本容量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>A-13.2</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>某组数据共 100 个，落在 [10, 20) 内的频数为 20，求该组的频率；若组距为 10，求直方图中该矩形的高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>A-13.2</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>某组数据的频率分布直方图中，各组 [0, 10)、[10, 20)、[20, 30)、[30, 40)、[40, 50) 的频率依次为 0.1、0.2、0.4、0.2、0.1。求众数、中位数与平均数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>A-13.2</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>某样本容量为 200，频率分布直方图中除某一组外，其余各组的频率之和为 0.85。求该组的频数；若该组组距为 20，求对应矩形的高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>A-13.3</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>例1</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>求数据 2、3、3、5、7 的平均数、中位数与众数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>A-13.3</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>例2</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>常考</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>求数据 2、3、3、5、7 的方差与标准差。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>A-13.3</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>例3</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>已知一组数据 x₁、x₂、…、xₙ 的平均数为 3，方差为 2。求数据 2x₁ + 1、2x₂ + 1、…、2xₙ + 1 的平均数与方差。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E64"/>
+  <autoFilter ref="A1:E124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3212,7 +5700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4491,8 +6979,1223 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>|a⃗| = √(a⃗ · a⃗)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>模与数量积</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>a⃗ · b⃗ = |a⃗||b⃗|cos θ</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>数量积定义</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>θ 为夹角</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>a⃗ ⊥ b⃗ ⟺ a⃗ · b⃗ = 0</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>垂直判定</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>非零向量</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>|a⃗ ± b⃗|² = |a⃗|² ± 2a⃗ · b⃗ + |b⃗|²</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>模的平方展开</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>a⃗ ∥ b⃗ ⟺ x₁y₂ − x₂y₁ = 0</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>平行判定</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>坐标形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>a⃗ ⊥ b⃗ ⟺ x₁x₂ + y₁y₂ = 0</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>垂直判定</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>坐标形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>|a⃗ · b⃗| ≤ |a⃗||b⃗|</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>柯西不等式</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>i² = −1</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>虚数单位</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>z · z̄ = |z|²</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>共轭与模</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>|z| = √(a² + b²)</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>复数的模</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>z = a + bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>z̄ 与 z 关于实轴对称</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>共轭的几何意义</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>|z₁ − z₂|</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>两点间距离</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>x = (−b ± i√(4ac − b²))/(2a)</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Δ &lt; 0 时的虚根</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>实系数方程</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>z = r(cos θ + i sin θ)</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>三角形式</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>r &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>zⁿ = rⁿ(cos nθ + i sin nθ)</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>棣莫弗定理</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>r &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>不共线三点确定一个平面</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>基本性质 2</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>三点不共线</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>两平面相交于一条直线</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>基本性质 3</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>有公共点</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>线面平行判定</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>面外线平行于面内线</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>线在面外</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>线面垂直判定</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>垂直于面内两条相交直线</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>两线相交</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>面面平行判定</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>面内两条相交直线平行于另一面</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>两线相交</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>面面垂直判定</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>一个面经过另一个面的垂线</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>线面角范围</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>斜线与射影所成角</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>[0°, 90°]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>二面角范围</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>两个半平面所成角</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>[0°, 180°]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>V = Sh</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>柱体体积</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>S 为底面积</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>V = Sh/3</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>锥体体积</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>S 为底面积</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>S侧 = 2πrh</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>圆柱侧面积</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>r 底面半径</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>S侧 = πrl</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>圆锥侧面积</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>l 为母线</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>S侧 = π(R + r)l</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>圆台侧面积</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>l 为母线</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>V = πh(R² + Rr + r²)/3</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>圆台体积</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>h 为高</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>S = 4πR²，V = 4πR³/3</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>球的表面积与体积</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>R 为球半径</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>r = √(R² − d²)</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>球的截面半径</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>d 为球心到截面距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>V − E + F = 2</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>欧拉公式</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>简单多面体</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>P(A) = m/n</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>古典概率</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>有限、等可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>P(Ā) = 1 − P(A)</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>对立事件</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>P(A ∪ B) = P(A) + P(B)</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>互斥事件加法</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>A、B 互斥</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>P(AB) = P(A)P(B)</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>独立事件乘法</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>A、B 独立</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>C(n, k)pᵏ(1 − p)ⁿ⁻ᵏ</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>独立重复试验</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>各次独立</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>P(至少一次) = 1 − (1 − p)ⁿ</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>至少一次</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>各次独立</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>x̄ = ∑xᵢ/n</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>平均数</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>s² = ∑(xᵢ − x̄)²/n</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>方差</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>s = √(s²)</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>标准差</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>数据加 a：均值 +a，方差不变</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>线性变换</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>数据乘 k：均值 ×k，方差 ×k²</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>线性变换</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>k ≠ 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>小矩形面积 = 频率</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>频率分布直方图</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>纵轴为频率/组距</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>n × Nᵢ/N</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>分层抽样各层人数</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>按比例抽样</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4503,7 +8206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5040,8 +8743,558 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A-7.3</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>延伸（三角函数 → 向量）</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>A-8.1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>A-8.2</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>递进（线性运算 → 数量积）</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A-8.2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>A-8.3</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>派生（数量积 → 坐标运算）</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>A-8.3</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>应用（坐标运算 → 几何应用）</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>延伸（向量 → 复数）</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>平面向量 · 单元八</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A-8.4</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>延伸（向量 → 复数）</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A-9.1</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>递进（代数运算 → 几何意义）</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A-9.2</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>派生（几何意义 → 三角形式）</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>延伸（复数 → 空间几何）</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>复数 · 单元九</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A-9.3</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>延伸（复数 → 空间几何）</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>A-10.1</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>A-10.2</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>递进（平面性质 → 线线关系）</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>A-10.2</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>A-10.3</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>递进（线线 → 线面）</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>A-10.3</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>递进（线面 → 面面）</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>应用（面面关系 → 几何体）</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>空间直线与平面 · 单元十</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>A-10.4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>应用（面面关系 → 柱体与锥体）</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>A-11.1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>A-11.2</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>递进（柱锥 → 多面体与旋转体）</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>A-11.2</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>递进（旋转体 → 球）</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>延伸（几何 → 概率）</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>简单几何体 · 单元十一</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>A-11.3</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>延伸（几何 → 概率）</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>A-12.1</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>A-12.2</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>递进（样本空间 → 古典概率）</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>A-12.2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>递进（古典概率 → 独立性）</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>延伸（概率 → 统计）</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>概率初步 · 单元十二</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>A-12.3</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>延伸（概率 → 统计）</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>A-13.1</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>A-13.2</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>递进（抽样 → 图表）</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>A-13.2</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>A-13.3</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>递进（图表 → 估计）</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>统计 · 单元十三</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5077,7 +9330,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7 个单元 / 21 个考点 / 63 道例题 / 46 条公式</t>
+          <t>13 个单元 / 41 个考点 / 123 道例题 / 91 条公式</t>
         </is>
       </c>
     </row>
